--- a/output/pdf_financials_xlsx/COR.xlsx
+++ b/output/pdf_financials_xlsx/COR.xlsx
@@ -1261,19 +1261,19 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.350703</v>
+        <v>-0.350703</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2.448268</v>
+        <v>-2.448268</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>2.457657</v>
+        <v>-2.457657</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>3.348016</v>
+        <v>-3.348016</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1.983788</v>
+        <v>-1.983788</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>-8.894188</v>
@@ -1561,19 +1561,19 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.350703</v>
+        <v>-0.350703</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>2.448268</v>
+        <v>-2.448268</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>2.457657</v>
+        <v>-2.457657</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>3.348016</v>
+        <v>-3.348016</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1.983788</v>
+        <v>-1.983788</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>-8.894188</v>
@@ -1735,19 +1735,19 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.350703</v>
+        <v>-0.350703</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2.448268</v>
+        <v>-2.448268</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>2.457657</v>
+        <v>-2.457657</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>3.348016</v>
+        <v>-3.348016</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>1.983788</v>
+        <v>-1.983788</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>-8.894188</v>
@@ -1931,13 +1931,13 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-61.441425</v>
+        <v>61.441425</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-66.96032</v>
+        <v>66.96032</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>-7.629954</v>
+        <v>7.629954</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>9.667596</v>
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.350703</v>
+        <v>-0.350703</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>2.448268</v>
+        <v>-2.448268</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>2.457657</v>
+        <v>-2.457657</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>3.348016</v>
+        <v>-3.348016</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>1.983788</v>
+        <v>-1.983788</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-8.894188</v>
@@ -2105,19 +2105,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.350703</v>
+        <v>-0.350703</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>2.448268</v>
+        <v>-2.448268</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>2.457657</v>
+        <v>-2.457657</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>3.348016</v>
+        <v>-3.348016</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>1.983788</v>
+        <v>-1.983788</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-8.894188</v>
@@ -2255,19 +2255,19 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>-0</v>
@@ -6047,49 +6047,49 @@
         <v>15.776906</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>10.881745</v>
+        <v>12.220615</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>13.28495</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>13.690427</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>14.299707</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>14.341567</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>14.848086</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.917329</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>2.588985</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>12.54915</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>14.770978</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>15.372891</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>15.602477</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>16.600462</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>18.591029</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>18.591029</v>
       </c>
       <c r="R92" s="1" t="inlineStr">
         <is>
@@ -10182,7 +10182,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -11805,7 +11809,11 @@
           <t>Reserves (note 7)</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>-</t>
@@ -13303,7 +13311,11 @@
           <t>Share based payment reserves 7(c)</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -14346,7 +14358,11 @@
           <t>Share based payment reserves 8(c)</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -15320,7 +15336,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
@@ -15413,7 +15433,11 @@
           <t>Share based payment reserves 9</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
@@ -15506,7 +15530,11 @@
           <t>Warrant reserves 9</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -16367,7 +16395,11 @@
           <t>Reserves 5</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
@@ -16456,7 +16488,11 @@
           <t>Share based payment reserves 5</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
           <t>-</t>
@@ -16547,7 +16583,11 @@
           <t>Warrant reserves 5</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>
@@ -51013,16 +51053,16 @@
         </is>
       </c>
       <c r="G430" s="5" t="n">
-        <v>2.457657</v>
+        <v>-2.457657</v>
       </c>
       <c r="H430" s="5" t="n">
-        <v>3.348016</v>
+        <v>-3.348016</v>
       </c>
       <c r="I430" s="5" t="n">
-        <v>1.983788</v>
+        <v>-1.983788</v>
       </c>
       <c r="J430" s="5" t="n">
-        <v>8.894188</v>
+        <v>-8.894188</v>
       </c>
       <c r="K430" t="inlineStr">
         <is>
@@ -52108,10 +52148,10 @@
         </is>
       </c>
       <c r="E441" s="5" t="n">
-        <v>0.350703</v>
+        <v>-0.350703</v>
       </c>
       <c r="F441" s="5" t="n">
-        <v>2.448268</v>
+        <v>-2.448268</v>
       </c>
       <c r="G441" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/COR.xlsx
+++ b/output/pdf_financials_xlsx/COR.xlsx
@@ -1035,46 +1035,46 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.07740900000000001</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.040689</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.02674</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.006542</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.000326</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.001825</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.007496</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.021855</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.001605</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.004756</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.017084</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.035641</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.043304</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.038218</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>0</v>
@@ -1995,46 +1995,46 @@
         <v>-2.448268</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.457657</v>
+        <v>-2.380248</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-3.348016</v>
+        <v>-3.307327</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.983788</v>
+        <v>-1.957048</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-8.894188</v>
+        <v>-8.900729999999999</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.38712</v>
+        <v>0.386794</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.327892</v>
+        <v>-0.329717</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-1.905409</v>
+        <v>-1.912905</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-1.261369</v>
+        <v>-1.283224</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.560406</v>
+        <v>-1.562011</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.917779</v>
+        <v>-0.922535</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-3.708258</v>
+        <v>-3.725342</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-5.120984</v>
+        <v>-5.156625</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-3.110624</v>
+        <v>-3.153928</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-2.974467</v>
+        <v>-3.012685</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>0.782181</v>
@@ -2111,46 +2111,46 @@
         <v>-2.448268</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.457657</v>
+        <v>-2.380248</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-3.348016</v>
+        <v>-3.307327</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.983788</v>
+        <v>-1.957048</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-8.894188</v>
+        <v>-8.900729999999999</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.38712</v>
+        <v>0.386794</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.327892</v>
+        <v>-0.329717</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-1.905409</v>
+        <v>-1.912905</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.261369</v>
+        <v>-1.283224</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.560406</v>
+        <v>-1.562011</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.917779</v>
+        <v>-0.922535</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-3.708258</v>
+        <v>-3.725342</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-5.120984</v>
+        <v>-5.156625</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-3.110624</v>
+        <v>-3.153928</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-2.974467</v>
+        <v>-3.012685</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>0.782181</v>
@@ -17179,7 +17179,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -40749,7 +40749,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -42563,7 +42563,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
@@ -44937,7 +44937,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
@@ -46307,7 +46307,7 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
@@ -47639,7 +47639,7 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
@@ -49130,7 +49130,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
@@ -50639,7 +50639,7 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
@@ -51237,7 +51237,7 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">

--- a/output/pdf_financials_xlsx/COR.xlsx
+++ b/output/pdf_financials_xlsx/COR.xlsx
@@ -2086,16 +2086,16 @@
         <v>0</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>0.06344900000000001</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0</v>
+        <v>0.08459899999999999</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>0</v>
+        <v>0.08459899999999999</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>0</v>
+        <v>0.02115</v>
       </c>
     </row>
     <row r="29">
@@ -2144,16 +2144,16 @@
         <v>-3.725342</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-5.156625</v>
+        <v>-5.093176</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-3.153928</v>
+        <v>-3.069329</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-3.012685</v>
+        <v>-2.928086</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>0.782181</v>
+        <v>0.803331</v>
       </c>
     </row>
     <row r="30">
@@ -6520,16 +6520,16 @@
         <v>0</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>0.06344900000000001</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>0.08459899999999999</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>0.08459899999999999</v>
       </c>
       <c r="R100" s="3" t="n">
-        <v>0</v>
+        <v>0.02115</v>
       </c>
     </row>
     <row r="101">
@@ -19419,7 +19419,11 @@
           <t>Depreciafion – right-of-use asset</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
           <t>-</t>
@@ -21807,7 +21811,11 @@
           <t>Depreciation – right-of-use asset</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
@@ -23739,7 +23747,11 @@
           <t>Depreciation – Right-of-use asset</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/COR.xlsx
+++ b/output/pdf_financials_xlsx/COR.xlsx
@@ -1264,7 +1264,7 @@
         <v>-0.350703</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-2.448268</v>
+        <v>-2.855626</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-2.457657</v>
@@ -1322,7 +1322,7 @@
         <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0</v>
+        <v>0.407358</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-0</v>
@@ -1992,7 +1992,7 @@
         <v>-0.350703</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.448268</v>
+        <v>-2.855626</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-2.380248</v>
@@ -2108,7 +2108,7 @@
         <v>-0.350703</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.448268</v>
+        <v>-2.855626</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-2.380248</v>
@@ -2258,7 +2258,7 @@
         <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-0</v>
+        <v>-14.26510334336499</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0</v>
@@ -18516,7 +18516,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>-</t>
@@ -37226,7 +37230,11 @@
           <t>Future income tax recovery (note 8)</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr"/>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E291" t="inlineStr">
         <is>
           <t>-</t>
@@ -52053,7 +52061,11 @@
           <t>Future income tax recovery (note 8)</t>
         </is>
       </c>
-      <c r="D440" t="inlineStr"/>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E440" t="inlineStr">
         <is>
           <t>-</t>
